--- a/test-output/BikeDetails.xlsx
+++ b/test-output/BikeDetails.xlsx
@@ -149,10 +149,10 @@
     <t>Hero Splendor Plus</t>
   </si>
   <si>
+    <t>Royal Enfield Classic 350</t>
+  </si>
+  <si>
     <t>Yamaha R15 V4</t>
-  </si>
-  <si>
-    <t>Royal Enfield Classic 350</t>
   </si>
   <si>
     <t>TVS Raider</t>
